--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="483">
   <si>
     <t>Filename</t>
   </si>
@@ -808,655 +808,661 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9967,0.0008,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0034,0.0003,0.0001,0.9991</t>
-  </si>
-  <si>
-    <t>0.9920,0.0004,0.0002,0.0034</t>
-  </si>
-  <si>
-    <t>0.7978,0.0003,0.0001,0.2357</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9825,0.0107,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.0006,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.9319,0.0007,0.0033,0.0388</t>
+  </si>
+  <si>
+    <t>0.5921,0.0002,0.0000,0.5673</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0017,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8868,0.0054,0.0693,0.0006</t>
+  </si>
+  <si>
+    <t>0.0355,0.0021,0.9735,0.0001</t>
+  </si>
+  <si>
+    <t>0.0582,0.0015,0.9676,0.0000</t>
+  </si>
+  <si>
+    <t>0.0061,0.0002,0.9938,0.0002</t>
+  </si>
+  <si>
+    <t>0.9238,0.0033,0.0591,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9991,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0116,0.9890,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7786,0.0002,0.3152,0.0002</t>
+  </si>
+  <si>
+    <t>0.0031,0.0009,0.9956,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0000,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0066,0.0007,0.9890,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9995,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9990,0.0004</t>
+  </si>
+  <si>
+    <t>0.0386,0.9516,0.0046,0.0013</t>
+  </si>
+  <si>
+    <t>0.9832,0.0088,0.0038,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0037,0.9994,0.0118</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.9673,0.0054,0.0164,0.0003</t>
+  </si>
+  <si>
+    <t>0.9710,0.0149,0.0064,0.0008</t>
+  </si>
+  <si>
+    <t>0.0999,0.9271,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9829,0.2944,0.0001</t>
+  </si>
+  <si>
+    <t>0.0041,0.8333,0.0901,0.0125</t>
+  </si>
+  <si>
+    <t>0.0080,0.0005,0.9644,0.0158</t>
+  </si>
+  <si>
+    <t>0.0099,0.0026,0.9835,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.2447,0.9853,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9993,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.5519,0.0003,0.9932</t>
+  </si>
+  <si>
+    <t>0.0002,0.9979,0.0033,0.0040</t>
+  </si>
+  <si>
+    <t>0.0003,0.9977,0.0283,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0041,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0007,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0174,0.9935,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.0003,0.9982,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0012,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.9688,0.0482,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0038,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0033,0.9992,0.0033</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0031,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9935,0.8567,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0015,0.9961,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0036,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9506,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9623,0.0002,0.0610,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9998,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9213,0.9952,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9905,0.9826,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0221,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9037,0.0000</t>
+  </si>
+  <si>
+    <t>0.0101,0.0001,0.0031,0.9924</t>
+  </si>
+  <si>
+    <t>0.0001,0.0012,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0020,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0034,0.0003,0.0019,0.9972</t>
+  </si>
+  <si>
+    <t>0.0029,0.0002,0.0006,0.9982</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0003,0.9959,0.0978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9919,0.9327,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9250,0.9855,0.0001</t>
+  </si>
+  <si>
+    <t>0.0043,0.0166,0.9772,0.0013</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.9872,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.5687,0.0000</t>
+  </si>
+  <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9975,0.0027,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9797,0.0009,0.0139,0.0002</t>
-  </si>
-  <si>
-    <t>0.0032,0.0021,0.9963,0.0003</t>
-  </si>
-  <si>
-    <t>0.0075,0.0002,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.0416,0.0004,0.9761,0.0001</t>
-  </si>
-  <si>
-    <t>0.9906,0.0007,0.0062,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0802,0.9580,0.0001,0.0000</t>
+    <t>0.9958,0.0050,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0007,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.9501,0.0008,0.0266,0.0015</t>
+  </si>
+  <si>
+    <t>0.0025,0.0001,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9988,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9987,0.0002,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.4182,0.0002,0.7086,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0006,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0062,0.0001,0.9958,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0121,0.0001,0.9941,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9987,0.0002</t>
-  </si>
-  <si>
-    <t>0.0220,0.9745,0.0021,0.0014</t>
-  </si>
-  <si>
-    <t>0.9745,0.0155,0.0054,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0011,0.9998,0.0124</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.9943,0.0054,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9889,0.0115,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.7589,0.2446,0.0057,0.0001</t>
-  </si>
-  <si>
-    <t>0.0051,0.9805,0.0473,0.0003</t>
-  </si>
-  <si>
-    <t>0.0058,0.6229,0.1652,0.0175</t>
-  </si>
-  <si>
-    <t>0.0035,0.0006,0.9413,0.0530</t>
-  </si>
-  <si>
-    <t>0.0004,0.0018,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0111,0.0670,0.9518,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0004,0.9981,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9134,0.0001,0.9867</t>
-  </si>
-  <si>
-    <t>0.0004,0.9979,0.0036,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0135,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0153,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0020,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0444,0.9954,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9998,0.0000</t>
+    <t>0.5504,0.5848,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.1681,0.0083,0.8044,0.0008</t>
+  </si>
+  <si>
+    <t>0.0942,0.0011,0.9332,0.0005</t>
+  </si>
+  <si>
+    <t>0.9799,0.0030,0.0039,0.0002</t>
+  </si>
+  <si>
+    <t>0.8811,0.0344,0.0131,0.0034</t>
+  </si>
+  <si>
+    <t>0.0069,0.0241,0.0079,0.9859</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0069,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.9745,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8755,0.1329,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.8985,0.1536,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0013,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0743,0.9970,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.4560,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0059,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.0009,0.9943,0.0003</t>
+  </si>
+  <si>
+    <t>0.9715,0.0012,0.0136,0.0002</t>
+  </si>
+  <si>
+    <t>0.8694,0.0013,0.0954,0.0012</t>
+  </si>
+  <si>
+    <t>0.1175,0.0001,0.9350,0.0003</t>
+  </si>
+  <si>
+    <t>0.8760,0.0007,0.1304,0.0006</t>
+  </si>
+  <si>
+    <t>0.3364,0.0001,0.0000,0.8419</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0220,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0001,0.9792,0.9533,0.0000</t>
+  </si>
+  <si>
+    <t>0.6131,0.5273,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.2816,0.8107,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9617,0.0003,0.0030,0.0216</t>
+  </si>
+  <si>
+    <t>0.0040,0.0041,0.9924,0.0039</t>
+  </si>
+  <si>
+    <t>0.9940,0.0010,0.0029,0.0006</t>
+  </si>
+  <si>
+    <t>0.9940,0.0001,0.0026,0.0011</t>
+  </si>
+  <si>
+    <t>0.0110,0.9894,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.7856,0.1762,0.0115,0.0019</t>
+  </si>
+  <si>
+    <t>0.9912,0.0004,0.0071,0.0001</t>
+  </si>
+  <si>
+    <t>0.2485,0.4946,0.0443,0.0032</t>
+  </si>
+  <si>
+    <t>0.9618,0.0054,0.0193,0.0001</t>
+  </si>
+  <si>
+    <t>0.9456,0.0180,0.0121,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0018,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9526,0.0591,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.5315,0.5756,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.9493,0.0584,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.0044,0.0550,0.9924,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0023,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.7213,0.3350,0.0021,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0010,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9798,0.0120,0.0038,0.0012</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0036,0.0137,0.9924,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0226,0.9977,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.9999,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0011,0.0005,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.9836,0.0186,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9834,0.0181,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.0019,0.0021,0.9983,0.0013</t>
-  </si>
-  <si>
-    <t>0.9989,0.0016,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9796,0.0361,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9876,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0032,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0010,0.9957,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9813,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9760,0.0000,0.0609,0.0000</t>
-  </si>
-  <si>
-    <t>0.4892,0.0007,0.5904,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0016,0.9991,0.0012</t>
-  </si>
-  <si>
-    <t>0.0000,0.9526,0.9937,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.9617,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0067,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.9885,0.0000</t>
-  </si>
-  <si>
-    <t>0.0194,0.0001,0.0007,0.9932</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0006,0.0007,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0019,0.0002,0.0011,0.9986</t>
-  </si>
-  <si>
-    <t>0.0010,0.0006,0.0005,0.9990</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.8416,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9942,0.6900,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9301,0.9916,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.0196,0.9665,0.0017</t>
-  </si>
-  <si>
-    <t>0.0000,0.9665,0.9962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9985,0.1094,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
+    <t>0.0002,0.0003,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.0049,0.0010,0.9933,0.0003</t>
+  </si>
+  <si>
+    <t>0.3690,0.0008,0.7249,0.0003</t>
+  </si>
+  <si>
+    <t>0.6571,0.0498,0.0747,0.0011</t>
+  </si>
+  <si>
+    <t>0.0072,0.0015,0.9902,0.0002</t>
+  </si>
+  <si>
+    <t>0.1136,0.0106,0.8280,0.0002</t>
+  </si>
+  <si>
+    <t>0.2545,0.0030,0.7486,0.0001</t>
+  </si>
+  <si>
+    <t>0.6526,0.0012,0.3555,0.0012</t>
+  </si>
+  <si>
+    <t>0.3408,0.0025,0.6426,0.0003</t>
+  </si>
+  <si>
+    <t>0.0096,0.9916,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.2646,0.8444,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.4537,0.6710,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9722,0.0415,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0932,0.9488,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9539,0.0313,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9936,0.0005,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.9923,0.0010,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.0053,0.0029,0.9917,0.0004</t>
+  </si>
+  <si>
+    <t>0.2848,0.0049,0.6786,0.0058</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9996,0.0013</t>
+  </si>
+  <si>
+    <t>0.0019,0.0026,0.9951,0.0004</t>
+  </si>
+  <si>
+    <t>0.0022,0.0146,0.9910,0.0005</t>
+  </si>
+  <si>
+    <t>0.0032,0.0020,0.9923,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0085,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0001,0.0003</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9993,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0019,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.9505,0.0008,0.0244,0.0024</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9992,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.9983,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0168,0.9894,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8672,0.0118,0.0587,0.0016</t>
-  </si>
-  <si>
-    <t>0.9450,0.0011,0.0512,0.0001</t>
-  </si>
-  <si>
-    <t>0.4878,0.0275,0.2989,0.0011</t>
-  </si>
-  <si>
-    <t>0.1119,0.1792,0.1880,0.0200</t>
-  </si>
-  <si>
-    <t>0.0023,0.0114,0.0244,0.9882</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.9885,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8945,0.1638,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.4293,0.6164,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0001,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.8494,0.9920,0.0001</t>
-  </si>
-  <si>
-    <t>0.0033,0.0749,0.9870,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0010,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0029,0.0009,0.9947,0.0001</t>
-  </si>
-  <si>
-    <t>0.9822,0.0009,0.0109,0.0002</t>
-  </si>
-  <si>
-    <t>0.4665,0.0004,0.6738,0.0001</t>
-  </si>
-  <si>
-    <t>0.0063,0.0007,0.9931,0.0008</t>
-  </si>
-  <si>
-    <t>0.0935,0.0030,0.9055,0.0005</t>
-  </si>
-  <si>
-    <t>0.0131,0.0005,0.0001,0.9962</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0119,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0009,0.0003,0.0004,0.9993</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.3342,0.0000</t>
-  </si>
-  <si>
-    <t>0.0745,0.9416,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9978,0.0008,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.7301,0.3979,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9254,0.0011,0.0071,0.0355</t>
-  </si>
-  <si>
-    <t>0.0008,0.0061,0.9977,0.0028</t>
-  </si>
-  <si>
-    <t>0.9894,0.0001,0.0030,0.0030</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0136,0.9785,0.0061,0.0007</t>
-  </si>
-  <si>
-    <t>0.9895,0.0027,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1832,0.6547,0.0378,0.0010</t>
-  </si>
-  <si>
-    <t>0.9355,0.0053,0.0346,0.0005</t>
-  </si>
-  <si>
-    <t>0.3082,0.2567,0.0911,0.0017</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9964,0.0019,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9807,0.0215,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.3162,0.7405,0.0029,0.0000</t>
-  </si>
-  <si>
-    <t>0.9830,0.0170,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0301,0.0340,0.9699,0.0005</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9963,0.0027,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9972,0.0021,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0011,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.9491,0.0457,0.0042,0.0003</t>
-  </si>
-  <si>
-    <t>0.0011,0.0002,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.0216,0.9945,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0074,0.9931,0.0012</t>
-  </si>
-  <si>
-    <t>0.0006,0.0019,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0440,0.0016,0.9559,0.0004</t>
-  </si>
-  <si>
-    <t>0.0742,0.0006,0.9454,0.0005</t>
-  </si>
-  <si>
-    <t>0.8126,0.0136,0.0805,0.0015</t>
-  </si>
-  <si>
-    <t>0.6506,0.0012,0.4076,0.0000</t>
-  </si>
-  <si>
-    <t>0.0110,0.2271,0.7614,0.0007</t>
-  </si>
-  <si>
-    <t>0.6358,0.0210,0.1888,0.0007</t>
-  </si>
-  <si>
-    <t>0.8692,0.0206,0.0402,0.0013</t>
-  </si>
-  <si>
-    <t>0.0183,0.0009,0.9782,0.0022</t>
-  </si>
-  <si>
-    <t>0.1227,0.9232,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0235,0.9850,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.4704,0.6918,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.7857,0.2948,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.4987,0.6182,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9771,0.0168,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9902,0.0010,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.1332,0.0050,0.8663,0.0002</t>
-  </si>
-  <si>
-    <t>0.0260,0.0027,0.9725,0.0017</t>
-  </si>
-  <si>
-    <t>0.0007,0.0013,0.9982,0.0042</t>
-  </si>
-  <si>
-    <t>0.0006,0.0047,0.9972,0.0003</t>
-  </si>
-  <si>
-    <t>0.0011,0.0094,0.9950,0.0005</t>
-  </si>
-  <si>
-    <t>0.0079,0.0007,0.9864,0.0011</t>
-  </si>
-  <si>
-    <t>0.0010,0.0025,0.9960,0.0005</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0000,0.0001</t>
+    <t>0.0001,0.0007,0.9998,0.0003</t>
+  </si>
+  <si>
+    <t>0.0087,0.0029,0.9900,0.0009</t>
+  </si>
+  <si>
+    <t>0.9914,0.0022,0.0042,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9997,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.0164,0.9974,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0012,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0028,0.9957,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.0052,0.9938,0.0013</t>
+  </si>
+  <si>
+    <t>0.8991,0.0014,0.0703,0.0010</t>
+  </si>
+  <si>
+    <t>0.0429,0.0001,0.9590,0.0007</t>
+  </si>
+  <si>
+    <t>0.9984,0.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9995,0.0005,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9985,0.0020,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0050,0.0125,0.9899,0.0009</t>
-  </si>
-  <si>
-    <t>0.9833,0.0011,0.0126,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0012,0.9987,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.1000,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0014,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0071,0.0017,0.9862,0.0005</t>
-  </si>
-  <si>
-    <t>0.0011,0.0032,0.9971,0.0007</t>
-  </si>
-  <si>
-    <t>0.8944,0.0027,0.0680,0.0019</t>
-  </si>
-  <si>
-    <t>0.8039,0.0001,0.3106,0.0002</t>
-  </si>
-  <si>
-    <t>0.9959,0.0002,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0223,0.0030,0.9654,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0019,0.9984,0.0002</t>
-  </si>
-  <si>
-    <t>0.0040,0.0034,0.9901,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0273,0.0023,0.8993,0.0103</t>
-  </si>
-  <si>
-    <t>0.1846,0.0013,0.7902,0.0015</t>
-  </si>
-  <si>
-    <t>0.0027,0.0002,0.9936,0.0021</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0028,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0119,0.0006,0.0006,0.9952</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9891,0.0005,0.0010,0.0017</t>
+    <t>0.0296,0.0082,0.9372,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0023,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0023,0.9974,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0036,0.0013,0.9920,0.0020</t>
+  </si>
+  <si>
+    <t>0.0913,0.0052,0.8670,0.0028</t>
+  </si>
+  <si>
+    <t>0.0011,0.0004,0.9967,0.0008</t>
+  </si>
+  <si>
+    <t>0.9947,0.0002,0.0005,0.0023</t>
+  </si>
+  <si>
+    <t>0.0002,0.0141,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0229,0.0006,0.0001,0.9935</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9811,0.0004,0.0002,0.0054</t>
   </si>
 </sst>
 </file>
@@ -1842,7 +1848,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1856,7 +1862,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1870,7 +1876,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1881,10 +1887,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1898,7 +1904,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1912,7 +1918,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1926,7 +1932,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1940,7 +1946,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1954,7 +1960,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1968,7 +1974,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1982,7 +1988,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1996,7 +2002,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2010,7 +2016,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2024,7 +2030,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2038,7 +2044,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2052,7 +2058,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2066,7 +2072,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2080,7 +2086,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2094,7 +2100,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2108,7 +2114,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2122,7 +2128,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2136,7 +2142,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2147,10 +2153,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2164,7 +2170,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2178,7 +2184,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2192,7 +2198,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2206,7 +2212,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2220,7 +2226,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2234,7 +2240,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2248,7 +2254,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2262,7 +2268,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2276,7 +2282,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2290,7 +2296,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2304,7 +2310,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2318,7 +2324,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2329,10 +2335,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2346,7 +2352,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2360,7 +2366,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2374,7 +2380,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2388,7 +2394,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2402,7 +2408,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2416,7 +2422,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2430,7 +2436,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2444,7 +2450,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2455,10 +2461,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2472,7 +2478,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2486,7 +2492,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2500,7 +2506,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2514,7 +2520,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2528,7 +2534,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2542,7 +2548,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2556,7 +2562,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2570,7 +2576,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2584,7 +2590,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2598,7 +2604,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2612,7 +2618,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>315</v>
+        <v>275</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2626,7 +2632,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2640,7 +2646,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2654,7 +2660,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>270</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2668,7 +2674,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2682,7 +2688,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2696,7 +2702,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2710,7 +2716,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2724,7 +2730,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2738,7 +2744,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2752,7 +2758,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2766,7 +2772,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2780,7 +2786,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>326</v>
+        <v>283</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2794,7 +2800,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2805,10 +2811,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2822,7 +2828,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2836,7 +2842,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2850,7 +2856,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2864,7 +2870,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2878,7 +2884,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2892,7 +2898,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2906,7 +2912,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2920,7 +2926,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2934,7 +2940,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2948,7 +2954,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2962,7 +2968,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2973,10 +2979,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2990,7 +2996,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3004,7 +3010,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3018,7 +3024,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3032,7 +3038,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3043,10 +3049,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3060,7 +3066,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3074,7 +3080,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>270</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3088,7 +3094,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>270</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3102,7 +3108,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>346</v>
+        <v>272</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3116,7 +3122,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3130,7 +3136,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3144,7 +3150,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>348</v>
+        <v>274</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3158,7 +3164,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>349</v>
+        <v>277</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3172,7 +3178,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3186,7 +3192,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3200,7 +3206,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3214,7 +3220,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3228,7 +3234,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3242,7 +3248,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>350</v>
+        <v>275</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3270,7 +3276,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3284,7 +3290,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3298,7 +3304,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3312,7 +3318,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3326,7 +3332,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3340,7 +3346,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3354,7 +3360,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3368,7 +3374,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3382,7 +3388,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3396,7 +3402,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3410,7 +3416,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3421,10 +3427,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D115" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3435,10 +3441,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3449,10 +3455,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3466,7 +3472,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3480,7 +3486,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3494,7 +3500,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3508,7 +3514,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3522,7 +3528,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>278</v>
+        <v>369</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3536,7 +3542,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3550,7 +3556,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3564,7 +3570,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3578,7 +3584,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3589,10 +3595,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3620,7 +3626,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3634,7 +3640,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>270</v>
+        <v>376</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3648,7 +3654,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3662,7 +3668,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>347</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3676,7 +3682,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3690,7 +3696,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3704,7 +3710,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3715,10 +3721,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3732,7 +3738,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3746,7 +3752,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3760,7 +3766,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3774,7 +3780,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3785,10 +3791,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3802,7 +3808,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3813,10 +3819,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3830,7 +3836,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3844,7 +3850,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3858,7 +3864,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3872,7 +3878,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3883,10 +3889,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3900,7 +3906,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>373</v>
+        <v>274</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3911,10 +3917,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D150" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3928,7 +3934,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3939,10 +3945,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3956,7 +3962,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3970,7 +3976,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3984,7 +3990,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3998,7 +4004,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4012,7 +4018,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4026,7 +4032,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4040,7 +4046,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4054,7 +4060,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4068,7 +4074,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4079,10 +4085,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4096,7 +4102,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4110,7 +4116,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4124,7 +4130,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>271</v>
+        <v>380</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4138,7 +4144,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4152,7 +4158,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>406</v>
+        <v>375</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4166,7 +4172,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4180,7 +4186,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>270</v>
+        <v>376</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4194,7 +4200,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4208,7 +4214,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4222,7 +4228,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>407</v>
+        <v>351</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4236,7 +4242,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4247,10 +4253,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D174" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4264,7 +4270,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4278,7 +4284,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4292,7 +4298,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4306,7 +4312,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4320,7 +4326,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>351</v>
+        <v>274</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4334,7 +4340,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4348,7 +4354,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4362,7 +4368,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4376,7 +4382,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4390,7 +4396,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4404,7 +4410,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4418,7 +4424,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4432,7 +4438,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4446,7 +4452,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4460,7 +4466,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4474,7 +4480,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4488,7 +4494,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4502,7 +4508,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4513,10 +4519,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4530,7 +4536,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4541,10 +4547,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4558,7 +4564,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4572,7 +4578,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4586,7 +4592,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4600,7 +4606,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4614,7 +4620,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4628,7 +4634,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4642,7 +4648,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4656,7 +4662,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4670,7 +4676,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4684,7 +4690,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4698,7 +4704,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4712,7 +4718,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4726,7 +4732,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4740,7 +4746,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4754,7 +4760,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4768,7 +4774,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4782,7 +4788,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4796,7 +4802,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>271</v>
+        <v>450</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4810,7 +4816,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>346</v>
+        <v>274</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4824,7 +4830,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4838,7 +4844,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>449</v>
+        <v>351</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4866,7 +4872,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>451</v>
+        <v>323</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4880,7 +4886,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>269</v>
+        <v>452</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4894,7 +4900,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4908,7 +4914,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4922,7 +4928,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4936,7 +4942,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4950,7 +4956,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4964,7 +4970,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4978,7 +4984,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4992,7 +4998,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5020,7 +5026,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>460</v>
+        <v>425</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5034,7 +5040,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5048,7 +5054,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5062,7 +5068,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5073,10 +5079,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5090,7 +5096,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5104,7 +5110,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>466</v>
+        <v>351</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5118,7 +5124,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5132,7 +5138,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5146,7 +5152,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>270</v>
+        <v>376</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5160,7 +5166,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>351</v>
+        <v>467</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5174,7 +5180,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>349</v>
+        <v>468</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5188,7 +5194,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5202,7 +5208,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5216,7 +5222,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5230,7 +5236,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5244,7 +5250,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5258,7 +5264,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5272,7 +5278,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5286,7 +5292,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5300,7 +5306,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5314,7 +5320,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5328,7 +5334,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5342,7 +5348,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5356,7 +5362,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5370,7 +5376,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>479</v>
+        <v>390</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5384,7 +5390,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5398,7 +5404,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
